--- a/ua-creatives/New_trend_new_product_ra_soat.xlsx
+++ b/ua-creatives/New_trend_new_product_ra_soat.xlsx
@@ -9,8 +9,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lỗi dữ liệu" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề xuất app mới" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DS đã có" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App mới đạt tiêu chí" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lọc AppstoreSpy" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App mới – đợt 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App mới đạt tiêu chí" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lọc AppstoreSpy" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'New product'!$A$1:$G$126</definedName>
@@ -28,7 +29,7 @@
     <numFmt numFmtId="167" formatCode="mm/dd"/>
     <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="57">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -283,6 +284,12 @@
       <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B54708"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -406,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -724,6 +731,14 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="52" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="52" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -52008,4613 +52023,4613 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>hidden camera detector</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>co.appnation.cameradetector</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>proxy (vpn)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>com.vpn.proxy.supervpn.freevpn.vpnproxy</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="0" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>love app for couple</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>ltd.love8.couples.relationship</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="0" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>alarm challenge</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>com.garageapp.alarmchallenges</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>petalo</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>com.pookies.food.ai</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>muslove</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>com.muzmatch.muzmatchapp</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>cat brush challenge</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>com.brushjjaemu.brushcat.challenge</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>themeart - widgets, app icons</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>com.themeart.icons.widgets</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="0" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>sticker dài hạn</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
+      <c r="B10" s="0" t="inlineStr"/>
+      <c r="C10" s="0" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>idol video call &amp; prank chat</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>com.idol.video.call.prank.chat.phone</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="0" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>cap money</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>6757230737</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="0" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>ai detector &amp; humanizer</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>io.zyur.wordect</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="0" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>dog identifier</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>com.dogidentifier.dogspot</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>study timer</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>com.superelement.pomodoro</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="0" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>subscription manager ( widget countdown )</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>com.alkapps.subx</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="0" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>cat dance filter challenge</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>com.greencat.aliencat.dance.filter</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="0" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>sticker maker (by draw)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>com.sticker.maker.custom.emoji.aistickerapp</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="0" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>dog translator (&amp;training)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>com.traini.app</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="0" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>cat translator</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>com.artpol.cat.translator</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="0" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>ai translator</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
+      <c r="B21" s="0" t="inlineStr"/>
+      <c r="C21" s="0" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>smiley fun live wallpaper</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>com.smiley.fun.live.wallpaper</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="0" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>rizz dating coach – ai flirt</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>com.flirgpt.app</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="0" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>ai note taker</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>com.recordpro.audiorecord</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="0" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>live video chat</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>com.secure.radio.push2talk.voicechat.random</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="0" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>emotional control</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
+      <c r="B26" s="0" t="inlineStr"/>
+      <c r="C26" s="0" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>love test filter</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
+      <c r="B27" s="0" t="inlineStr"/>
+      <c r="C27" s="0" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>speaker cleaner</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>com.tranquilpartner.soniccleaner</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="0" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>piano</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
+      <c r="B29" s="0" t="inlineStr"/>
+      <c r="C29" s="0" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>tarot ai</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>ai.onlineastrology.tarot</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="0" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>video maker</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>instagramstory.maker.playvo</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="0" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>recovery lost photo/message/video</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>com.bitcraft.allrecoveryfiles</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="0" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>emoji keyboard</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>com.simejikeyboard</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="0" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>easy homescreen</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>easy.launcher</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="0" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>film camera - vintage camera</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>filmcamera.vintagecamera.digitalcamera.retrocamera</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="0" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>ai astrology</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>com.ojassoft.astrosage</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="0" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>mangatoon: đọc truyện chat</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>mobi.mangatoon.comics.aphone</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="0" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>spin master</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
+      <c r="B38" s="0" t="inlineStr"/>
+      <c r="C38" s="0" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>baby translator</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>com.babytranslator.bankr0t</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="0" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>caller id</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>com.peekdial.unseen.chat.read.message.private</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="0" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>gps camera &amp; live earth map</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>com.gpsmap.camera.location.navigation.tracker.findfriends</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="0" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>phone ringtone &amp; calling wallpapers</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>com.phonetheme.callscreen.theme</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="0" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>tier list maker</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>com.tiermaker.app</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="0" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>cue - smart ai meeting notes</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>ai.forty4pixels.voices</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="0" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>ai question answer</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>com.odamobil.blackboard.ai</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="0" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>interview pilot: ai interview copilot</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>com.liberace.interviewpilot</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="0" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>puretune: offline music</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>com.puretunemusic.radio</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="0" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>blood sugar care: bp monitor</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>bp.bloodapp.surga.bloodtracker.app</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="0" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>prank sound &amp; prank voice</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>com.pranksound.airhorn.funnysound.app</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="0" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>lightnovel</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>com.matmacn.skdbn.almost</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="0" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>astrolokal</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>com.astrolokal.astrology</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="0" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>ai song generator</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>co.twowise.jukebox</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="0" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>peachy: face app &amp; body editor</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>peachy.bodyeditor.faceapp</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="0" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>football live scores</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>com.tapgoal.football.livescore.stats</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="0" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>live scores: football match</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>com.football.live.scores.match.soccer</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="0" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>airlearn - language learning</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>com.unacademy.antonio</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="0" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="0" t="inlineStr">
         <is>
           <t>palmistry - ai palm reader</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>com.zodiac.horoscope.palmreader.scanpalmistry</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="0" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
         <is>
           <t>screen drawing</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>ltd.love8.couples.relationship</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="0" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
         <is>
           <t>online betting</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>com.betway.scores.android</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="0" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="0" t="inlineStr">
         <is>
           <t>body scanner</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>com.xrayscanner.allbodyinfo.humanspecies</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="0" t="n">
         <v>61</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="0" t="inlineStr">
         <is>
           <t>ai outfit try on</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>com.aioutfit.tryon.app</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="0" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="0" t="inlineStr">
         <is>
           <t>cute keyboard: sound &amp; emoji</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>com.emoji.cutekeyboard.themes.fontkeyboard</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="0" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="0" t="inlineStr">
         <is>
           <t>battery charging effect screen</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="n">
+      <c r="B63" s="0" t="inlineStr"/>
+      <c r="C63" s="0" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="0" t="inlineStr">
         <is>
           <t>broken screen prank &amp; sound</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="n">
+      <c r="B64" s="0" t="inlineStr"/>
+      <c r="C64" s="0" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>caller id</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="n">
+      <c r="B65" s="0" t="inlineStr"/>
+      <c r="C65" s="0" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
         <is>
           <t>future face – ai age changer</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>com.facephoto.retouch.facelab.aging</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="0" t="n">
         <v>67</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="0" t="inlineStr">
         <is>
           <t>my sivi ai</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>com.practice.ninja_study</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="0" t="n">
         <v>68</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="0" t="inlineStr">
         <is>
           <t>ai home</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>com.interiordesign.home.decorai</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="0" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="0" t="inlineStr">
         <is>
           <t>fff diamond: skins &amp; emotes</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>com.hh.ffdiamond.dailyguide</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="0" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="0" t="inlineStr">
         <is>
           <t>reverse image search finder</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>com.appdroid.searchbylens</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="0" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="0" t="inlineStr">
         <is>
           <t>miracast : cast screen on tv</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>com.casttv.screentv.mirroring.app</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="0" t="n">
         <v>73</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="0" t="inlineStr">
         <is>
           <t>babygenie - ai baby generator</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>com.fumaomao.genie.baby</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="0" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="0" t="inlineStr">
         <is>
           <t>grammar check by ai writing</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>ai.metaverselabs.grammargpt</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="0" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="0" t="inlineStr">
         <is>
           <t>go fly drone camera controller</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>com.smartwidgetlabs.djidrone</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="0" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
         <is>
           <t>nfc tag: card reader &amp; scanner</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>com.smartwidgetlabs.nfctools</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="0" t="n">
         <v>77</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="0" t="inlineStr">
         <is>
           <t>print document: mobile printer</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>com.documents.easyprint.scanner.smartprinter.mobileprint</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="0" t="n">
         <v>78</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="0" t="inlineStr">
         <is>
           <t>goallive: world cup 2026 news</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="0" t="inlineStr">
         <is>
           <t>com.drava.goallive.scores.wc26</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="0" t="n">
         <v>79</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="0" t="inlineStr">
         <is>
           <t>ai mirror: screen mirroring tv</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>com.mirroring.app.casttv</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="0" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="0" t="inlineStr">
         <is>
           <t>game emulator: gb4 retro games</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="0" t="inlineStr">
         <is>
           <t>com.game.emulator.gb4.retro.gameboy.collection</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="0" t="n">
         <v>81</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="0" t="inlineStr">
         <is>
           <t>fluid wallpaper - relax slime</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>com.magic.fluid.live.wallpaper.slime.simulator.asmr.antistress</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="0" t="n">
         <v>82</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="0" t="inlineStr">
         <is>
           <t>find my phone with clap sound</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="0" t="inlineStr">
         <is>
           <t>com.myfuturecode.clapsense</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="0" t="n">
         <v>83</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="0" t="inlineStr">
         <is>
           <t>tota ai: talk to your dost</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t>com.primetrace.companion.tota.ai</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="0" t="n">
         <v>84</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="0" t="inlineStr">
         <is>
           <t>hairgenie - ai hair generator</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="0" t="inlineStr">
         <is>
           <t>com.fumaomao.hairgenie</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="0" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="0" t="inlineStr">
         <is>
           <t>sherlock – ai face search</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>com.robomanager.ai.facesearch</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="0" t="n">
         <v>86</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="0" t="inlineStr">
         <is>
           <t>app lock</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="0" t="inlineStr">
         <is>
           <t>com.asianmobile.voicelock.applock</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="0" t="n">
         <v>87</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="0" t="inlineStr">
         <is>
           <t>litsticker</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="0" t="inlineStr">
         <is>
           <t>1472619338</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="0" t="n">
         <v>88</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="0" t="inlineStr">
         <is>
           <t>antivirus</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="0" t="inlineStr">
         <is>
           <t>com.grouprx.pureanti</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="0" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="0" t="inlineStr">
         <is>
           <t>hd camera - sweet beauty</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="0" t="inlineStr">
         <is>
           <t>com.photoeditor.beauty.camera.hdcamera</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="0" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="0" t="inlineStr">
         <is>
           <t>stepreward: walk &amp; earn</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="0" t="inlineStr">
         <is>
           <t>com.iwanmaket.walk.stepreward</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="0" t="n">
         <v>91</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="0" t="inlineStr">
         <is>
           <t>dance ai: dance video maker</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="0" t="inlineStr">
         <is>
           <t>com.aidance.videomaker.videogenerator</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="0" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="0" t="inlineStr">
         <is>
           <t>face aging - age calculator</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="n">
+      <c r="B91" s="0" t="inlineStr"/>
+      <c r="C91" s="0" t="n">
         <v>93</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="0" t="inlineStr">
         <is>
           <t>photo gear</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="0" t="inlineStr">
         <is>
           <t>1459953293</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="0" t="n">
         <v>94</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="0" t="inlineStr">
         <is>
           <t>self-care pet</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="0" t="inlineStr">
         <is>
           <t>com.musa.musa</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="0" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="0" t="inlineStr">
         <is>
           <t>ps remote game controller</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="0" t="inlineStr">
         <is>
           <t>com.game.ps.remote.play.controller.emulator.stream</t>
         </is>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="0" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="0" t="inlineStr">
         <is>
           <t>volume booster - sound booster</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="0" t="inlineStr">
         <is>
           <t>volumebooster.soundspeaker.louder</t>
         </is>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="0" t="n">
         <v>97</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="0" t="inlineStr">
         <is>
           <t>wifi password</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="0" t="inlineStr">
         <is>
           <t>com.manager.wifi.connection.network</t>
         </is>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="0" t="n">
         <v>98</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="0" t="inlineStr">
         <is>
           <t>loopit</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="0" t="inlineStr">
         <is>
           <t>com.seedleap.loopitapp</t>
         </is>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="0" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="0" t="inlineStr">
         <is>
           <t>polybuzz: chat with ai friends</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="0" t="inlineStr">
         <is>
           <t>ai.socialapps.speakmaster</t>
         </is>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="0" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="0" t="inlineStr">
         <is>
           <t>daily bhakti</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>co.dailybhakti.app</t>
         </is>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="0" t="n">
         <v>101</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="0" t="inlineStr">
         <is>
           <t>daily bible: widgets &amp; prayer</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="0" t="inlineStr">
         <is>
           <t>life.growly.dailybible</t>
         </is>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="0" t="n">
         <v>102</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="0" t="inlineStr">
         <is>
           <t>parakeet ai interview</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="0" t="inlineStr">
         <is>
           <t>com.epiphyllum.carani.app</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="0" t="n">
         <v>103</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="0" t="inlineStr">
         <is>
           <t>setlog</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>com.newchat.setlog</t>
         </is>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="0" t="n">
         <v>104</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="0" t="inlineStr">
         <is>
           <t>ai palmistry: life palm reader</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
         <is>
           <t>com.astrotech.aipalmistry.palmreader.app</t>
         </is>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="0" t="n">
         <v>105</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="0" t="inlineStr">
         <is>
           <t>tv remote</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="0" t="inlineStr">
         <is>
           <t>com.tv.remote.cct</t>
         </is>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="0" t="n">
         <v>106</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="0" t="inlineStr">
         <is>
           <t>caller id trusted call &amp; block</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>com.trusted.call.sms.block.callerid</t>
         </is>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="0" t="n">
         <v>107</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="0" t="inlineStr">
         <is>
           <t>dj music mix</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="n">
+      <c r="B106" s="0" t="inlineStr"/>
+      <c r="C106" s="0" t="n">
         <v>108</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="0" t="inlineStr">
         <is>
           <t>ios launcher</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="n">
+      <c r="B107" s="0" t="inlineStr"/>
+      <c r="C107" s="0" t="n">
         <v>109</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="0" t="inlineStr">
         <is>
           <t>scary prank call &amp; fake chat</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="0" t="inlineStr">
         <is>
           <t>com.scary.prankcall.horror.fake.video</t>
         </is>
       </c>
-      <c r="C108" t="n">
+      <c r="C108" s="0" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="0" t="inlineStr">
         <is>
           <t>baby &amp; pregnancy tracker app</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="0" t="inlineStr">
         <is>
           <t>com.bellybloom.pregnancy.tracker</t>
         </is>
       </c>
-      <c r="C109" t="n">
+      <c r="C109" s="0" t="n">
         <v>111</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="0" t="inlineStr">
         <is>
           <t>flashlight : flash alert &amp; led</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="0" t="inlineStr">
         <is>
           <t>com.flashapp.led.banner.app</t>
         </is>
       </c>
-      <c r="C110" t="n">
+      <c r="C110" s="0" t="n">
         <v>112</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="0" t="inlineStr">
         <is>
           <t>livestamp: photo stamps</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="0" t="inlineStr">
         <is>
           <t>com.livestamp.android</t>
         </is>
       </c>
-      <c r="C111" t="n">
+      <c r="C111" s="0" t="n">
         <v>113</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="0" t="inlineStr">
         <is>
           <t>lockscreen drawing</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="0" t="inlineStr">
         <is>
           <t>com.ezt.lockscreen.draw</t>
         </is>
       </c>
-      <c r="C112" t="n">
+      <c r="C112" s="0" t="n">
         <v>114</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="0" t="inlineStr">
         <is>
           <t>widgetable: besties &amp; couples</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="0" t="inlineStr">
         <is>
           <t>com.widgetable.theme.android</t>
         </is>
       </c>
-      <c r="C113" t="n">
+      <c r="C113" s="0" t="n">
         <v>115</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="0" t="inlineStr">
         <is>
           <t>dress challenge</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>com.dress.filter.impress.challenge.funny.rank</t>
         </is>
       </c>
-      <c r="C114" t="n">
+      <c r="C114" s="0" t="n">
         <v>116</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="0" t="inlineStr">
         <is>
           <t>falling loop filter challenge</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="0" t="inlineStr">
         <is>
           <t>com.nexify.falling.loop.filter.funny.video</t>
         </is>
       </c>
-      <c r="C115" t="n">
+      <c r="C115" s="0" t="n">
         <v>117</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="0" t="inlineStr">
         <is>
           <t>ai baby generator</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="0" t="inlineStr">
         <is>
           <t>com.fumaomao.genie.baby</t>
         </is>
       </c>
-      <c r="C116" t="n">
+      <c r="C116" s="0" t="n">
         <v>118</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="0" t="inlineStr">
         <is>
           <t>ai community</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="0" t="inlineStr">
         <is>
           <t>com.weaver.app.prod</t>
         </is>
       </c>
-      <c r="C117" t="n">
+      <c r="C117" s="0" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="0" t="inlineStr">
         <is>
           <t>emoji battery &amp; shimeji pet</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t>com.anime.shimeji.petonscreen</t>
         </is>
       </c>
-      <c r="C118" t="n">
+      <c r="C118" s="0" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="0" t="inlineStr">
         <is>
           <t>followers &amp; unfollowers</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="0" t="inlineStr">
         <is>
           <t>com.insta.follower</t>
         </is>
       </c>
-      <c r="C119" t="n">
+      <c r="C119" s="0" t="n">
         <v>121</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="0" t="inlineStr">
         <is>
           <t>themebox - app icons, widgets</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="0" t="inlineStr">
         <is>
           <t>com.themebox.icons.widgets</t>
         </is>
       </c>
-      <c r="C120" t="n">
+      <c r="C120" s="0" t="n">
         <v>122</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="0" t="inlineStr">
         <is>
           <t>calorie counter</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="0" t="inlineStr">
         <is>
           <t>io.foodvisor.foodvisor</t>
         </is>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" s="0" t="n">
         <v>123</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="0" t="inlineStr">
         <is>
           <t>screen recorder: video editor</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="0" t="inlineStr">
         <is>
           <t>com.fumaomao.record</t>
         </is>
       </c>
-      <c r="C122" t="n">
+      <c r="C122" s="0" t="n">
         <v>124</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="0" t="inlineStr">
         <is>
           <t>anti theft alarm for phone</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="0" t="inlineStr">
         <is>
           <t>antitheftalarm.donttouchmyphone.antipro</t>
         </is>
       </c>
-      <c r="C123" t="n">
+      <c r="C123" s="0" t="n">
         <v>125</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="0" t="inlineStr">
         <is>
           <t>zipper lock screen &amp; wallpaper</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="0" t="inlineStr">
         <is>
           <t>zipper.lockscreens.customize.wallpaper</t>
         </is>
       </c>
-      <c r="C124" t="n">
+      <c r="C124" s="0" t="n">
         <v>126</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="0" t="inlineStr">
         <is>
           <t>lurk: secure private browser</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="0" t="inlineStr">
         <is>
           <t>com.secure.privatebrowser.vpnbrowser.videodownloader</t>
         </is>
       </c>
-      <c r="C125" t="n">
+      <c r="C125" s="0" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="0" t="inlineStr">
         <is>
           <t>diy wallpaper maker collage</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="0" t="inlineStr">
         <is>
           <t>com.diy.wallpaper.maker.collage</t>
         </is>
       </c>
-      <c r="C126" t="n">
+      <c r="C126" s="0" t="n">
         <v>129</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="0" t="inlineStr">
         <is>
           <t>auto tapper &amp; touch clicker</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="0" t="inlineStr">
         <is>
           <t>com.auto.clicker.tap.assistant.tool</t>
         </is>
       </c>
-      <c r="C127" t="n">
+      <c r="C127" s="0" t="n">
         <v>130</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="0" t="inlineStr">
         <is>
           <t>ai music studio</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="0" t="inlineStr">
         <is>
           <t>ai.seatunes.com</t>
         </is>
       </c>
-      <c r="C128" t="n">
+      <c r="C128" s="0" t="n">
         <v>132</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="0" t="inlineStr">
         <is>
           <t>multiple accounts: dual space</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="0" t="inlineStr">
         <is>
           <t>com.excelliance.multiaccounts</t>
         </is>
       </c>
-      <c r="C129" t="n">
+      <c r="C129" s="0" t="n">
         <v>133</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="0" t="inlineStr">
         <is>
           <t>meet &amp; chat: find soul</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="0" t="inlineStr">
         <is>
           <t>com.kukie</t>
         </is>
       </c>
-      <c r="C130" t="n">
+      <c r="C130" s="0" t="n">
         <v>134</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="0" t="inlineStr">
         <is>
           <t>hidden camera detector spy cam</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="0" t="inlineStr">
         <is>
           <t>com.spycamera.hiddencamerafinder.spycamdetector.hiddencameradetector</t>
         </is>
       </c>
-      <c r="C131" t="n">
+      <c r="C131" s="0" t="n">
         <v>135</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="0" t="inlineStr">
         <is>
           <t>my little pomodoro: focus time</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="0" t="inlineStr">
         <is>
           <t>net.devfloor.pomodor</t>
         </is>
       </c>
-      <c r="C132" t="n">
+      <c r="C132" s="0" t="n">
         <v>136</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="0" t="inlineStr">
         <is>
           <t>cam translate pro, ai keyboard</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="0" t="inlineStr">
         <is>
           <t>com.translateall.photocamtranslator.translationtools</t>
         </is>
       </c>
-      <c r="C133" t="n">
+      <c r="C133" s="0" t="n">
         <v>138</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="0" t="inlineStr">
         <is>
           <t>ar dogy: funny meme filter</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="0" t="inlineStr">
         <is>
           <t>com.translateall.photocamtranslator.translationtools</t>
         </is>
       </c>
-      <c r="C134" t="n">
+      <c r="C134" s="0" t="n">
         <v>139</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="0" t="inlineStr">
         <is>
           <t>gps photo stamp map camera</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="0" t="inlineStr">
         <is>
           <t>com.gpscamera.photolocation.locationstamp.map</t>
         </is>
       </c>
-      <c r="C135" t="n">
+      <c r="C135" s="0" t="n">
         <v>140</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="0" t="inlineStr">
         <is>
           <t>miracast app : cast to tv</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" s="0" t="inlineStr">
         <is>
           <t>cast.tvwatching.app</t>
         </is>
       </c>
-      <c r="C136" t="n">
+      <c r="C136" s="0" t="n">
         <v>141</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="0" t="inlineStr">
         <is>
           <t>playit-all in one video player</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" s="0" t="inlineStr">
         <is>
           <t>com.playit.videoplayer</t>
         </is>
       </c>
-      <c r="C137" t="n">
+      <c r="C137" s="0" t="n">
         <v>142</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="0" t="inlineStr">
         <is>
           <t>popsa-print your photos</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" s="0" t="inlineStr">
         <is>
           <t>com.popsa.android</t>
         </is>
       </c>
-      <c r="C138" t="n">
+      <c r="C138" s="0" t="n">
         <v>143</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="0" t="inlineStr">
         <is>
           <t>emoji battery icon customize</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="n">
+      <c r="B139" s="0" t="inlineStr"/>
+      <c r="C139" s="0" t="n">
         <v>144</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="0" t="inlineStr">
         <is>
           <t>remind - random reminder</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B140" s="0" t="inlineStr">
         <is>
           <t>com.spacewire.bhaktilok</t>
         </is>
       </c>
-      <c r="C140" t="n">
+      <c r="C140" s="0" t="n">
         <v>145</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="0" t="inlineStr">
         <is>
           <t>ai voice lock screen - voiceos</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="0" t="inlineStr">
         <is>
           <t>com.voice.lock.screen.phone</t>
         </is>
       </c>
-      <c r="C141" t="n">
+      <c r="C141" s="0" t="n">
         <v>146</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="0" t="inlineStr">
         <is>
           <t>ez pose - photo pose guide</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="0" t="inlineStr">
         <is>
           <t>com.boba.ezpose</t>
         </is>
       </c>
-      <c r="C142" t="n">
+      <c r="C142" s="0" t="n">
         <v>147</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="0" t="inlineStr">
         <is>
           <t>scrl: photo collage maker</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="0" t="inlineStr">
         <is>
           <t>1289057196</t>
         </is>
       </c>
-      <c r="C143" t="n">
+      <c r="C143" s="0" t="n">
         <v>149</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="0" t="inlineStr">
         <is>
           <t>noodle: animate your doodles</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="0" t="inlineStr">
         <is>
           <t>6499508227</t>
         </is>
       </c>
-      <c r="C144" t="n">
+      <c r="C144" s="0" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="0" t="inlineStr">
         <is>
           <t>dayframe: aesthetic recaps</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="0" t="inlineStr">
         <is>
           <t>6764794279</t>
         </is>
       </c>
-      <c r="C145" t="n">
+      <c r="C145" s="0" t="n">
         <v>151</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="0" t="inlineStr">
         <is>
           <t>chalo - live bus tracking app</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B146" s="0" t="inlineStr">
         <is>
           <t>app.zophop</t>
         </is>
       </c>
-      <c r="C146" t="n">
+      <c r="C146" s="0" t="n">
         <v>152</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="0" t="inlineStr">
         <is>
           <t>bergfex: hiking &amp; tracking</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B147" s="0" t="inlineStr">
         <is>
           <t>com.bergfex.tour</t>
         </is>
       </c>
-      <c r="C147" t="n">
+      <c r="C147" s="0" t="n">
         <v>153</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="0" t="inlineStr">
         <is>
           <t>fun xray body scanner</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B148" s="0" t="inlineStr">
         <is>
           <t>com.bodyscanner.fullbodyscan.allbodypart.xrayvision</t>
         </is>
       </c>
-      <c r="C148" t="n">
+      <c r="C148" s="0" t="n">
         <v>154</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="0" t="inlineStr">
         <is>
           <t>emoji battery icon customize</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B149" s="0" t="inlineStr">
         <is>
           <t>com.tstudio.emojibatteryicon</t>
         </is>
       </c>
-      <c r="C149" t="n">
+      <c r="C149" s="0" t="n">
         <v>155</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="0" t="inlineStr">
         <is>
           <t>ai music studio</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="0" t="inlineStr">
         <is>
           <t>ai.seatunes.com</t>
         </is>
       </c>
-      <c r="C150" t="n">
+      <c r="C150" s="0" t="n">
         <v>156</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="0" t="inlineStr">
         <is>
           <t>weather now</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="0" t="inlineStr">
         <is>
           <t>com.weather.now.radar.alerts</t>
         </is>
       </c>
-      <c r="C151" t="n">
+      <c r="C151" s="0" t="n">
         <v>157</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="0" t="inlineStr">
         <is>
           <t>broken screen</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" s="0" t="inlineStr">
         <is>
           <t>brokenscreen.prank.on.touch.crackscreen</t>
         </is>
       </c>
-      <c r="C152" t="n">
+      <c r="C152" s="0" t="n">
         <v>158</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="0" t="inlineStr">
         <is>
           <t>nova match: soulmate sketch</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="0" t="inlineStr">
         <is>
           <t>com.soulmatesketch.astradraw.app</t>
         </is>
       </c>
-      <c r="C153" t="n">
+      <c r="C153" s="0" t="n">
         <v>159</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="0" t="inlineStr">
         <is>
           <t>daily drink tracker app</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" s="0" t="inlineStr">
         <is>
           <t>com.brewwww.myapp</t>
         </is>
       </c>
-      <c r="C154" t="n">
+      <c r="C154" s="0" t="n">
         <v>160</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="0" t="inlineStr">
         <is>
           <t>ai clothes changer</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="0" t="inlineStr">
         <is>
           <t>com.ai.tryonclothes.photo.model.generator</t>
         </is>
       </c>
-      <c r="C155" t="n">
+      <c r="C155" s="0" t="n">
         <v>161</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="0" t="inlineStr">
         <is>
           <t>camera tuner (improve camera quality)</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B156" s="0" t="inlineStr">
         <is>
           <t>com.motorola.imagertuning_w</t>
         </is>
       </c>
-      <c r="C156" t="n">
+      <c r="C156" s="0" t="n">
         <v>162</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="0" t="inlineStr">
         <is>
           <t>magic hand: ar control effects</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" s="0" t="inlineStr">
         <is>
           <t>com.control.magic.hand.ar.effects</t>
         </is>
       </c>
-      <c r="C157" t="n">
+      <c r="C157" s="0" t="n">
         <v>163</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="0" t="inlineStr">
         <is>
           <t>tarot reader: daily tarot read</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="0" t="inlineStr">
         <is>
           <t>com.tarot.astrology.horoscope.daily.pro</t>
         </is>
       </c>
-      <c r="C158" t="n">
+      <c r="C158" s="0" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="0" t="inlineStr">
         <is>
           <t>remove background &amp; object</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" s="0" t="inlineStr">
         <is>
           <t>com.backgroundremover.editbackground.removeobject</t>
         </is>
       </c>
-      <c r="C159" t="n">
+      <c r="C159" s="0" t="n">
         <v>165</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="0" t="inlineStr">
         <is>
           <t>shanti club</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B160" s="0" t="inlineStr">
         <is>
           <t>com.capslock.shanticlub</t>
         </is>
       </c>
-      <c r="C160" t="n">
+      <c r="C160" s="0" t="n">
         <v>166</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="0" t="inlineStr">
         <is>
           <t>moto camera tuner a16</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B161" s="0" t="inlineStr">
         <is>
           <t>com.motorola.imagertuning_w</t>
         </is>
       </c>
-      <c r="C161" t="n">
+      <c r="C161" s="0" t="n">
         <v>167</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="0" t="inlineStr">
         <is>
           <t>beauty scanner - face score ai</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B162" s="0" t="inlineStr">
         <is>
           <t>com.golden.ratio.face</t>
         </is>
       </c>
-      <c r="C162" t="n">
+      <c r="C162" s="0" t="n">
         <v>168</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="0" t="inlineStr">
         <is>
           <t>equal ai - ai call assistant</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B163" s="0" t="inlineStr">
         <is>
           <t>in.equal.ai.assistant</t>
         </is>
       </c>
-      <c r="C163" t="n">
+      <c r="C163" s="0" t="n">
         <v>169</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="0" t="inlineStr">
         <is>
           <t>locksreen calendar</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B164" s="0" t="inlineStr">
         <is>
           <t>6758650351</t>
         </is>
       </c>
-      <c r="C164" t="n">
+      <c r="C164" s="0" t="n">
         <v>170</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="0" t="inlineStr">
         <is>
           <t>daily food diary &amp; log app</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" s="0" t="inlineStr">
         <is>
           <t>6759185418</t>
         </is>
       </c>
-      <c r="C165" t="n">
+      <c r="C165" s="0" t="n">
         <v>171</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="0" t="inlineStr">
         <is>
           <t>stampify: photo stamp maker</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B166" s="0" t="inlineStr">
         <is>
           <t>xyz.otterspark.stampify</t>
         </is>
       </c>
-      <c r="C166" t="n">
+      <c r="C166" s="0" t="n">
         <v>172</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="0" t="inlineStr">
         <is>
           <t>ai meal</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B167" s="0" t="inlineStr">
         <is>
           <t>com.eatr.eatr</t>
         </is>
       </c>
-      <c r="C167" t="n">
+      <c r="C167" s="0" t="n">
         <v>173</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="0" t="inlineStr">
         <is>
           <t>kibori: sticker, meme keyboard</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B168" s="0" t="inlineStr">
         <is>
           <t>6746079579</t>
         </is>
       </c>
-      <c r="C168" t="n">
+      <c r="C168" s="0" t="n">
         <v>174</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="0" t="inlineStr">
         <is>
           <t>usly: cute couple widgets</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B169" s="0" t="inlineStr">
         <is>
           <t>6789082469</t>
         </is>
       </c>
-      <c r="C169" t="n">
+      <c r="C169" s="0" t="n">
         <v>175</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="0" t="inlineStr">
         <is>
           <t>antiqsnap: antique identifier</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B170" s="0" t="inlineStr">
         <is>
           <t>com.antiqueworth.identifier</t>
         </is>
       </c>
-      <c r="C170" t="n">
+      <c r="C170" s="0" t="n">
         <v>176</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="0" t="inlineStr">
         <is>
           <t>donna ai song &amp; music maker</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B171" s="0" t="inlineStr">
         <is>
           <t>com.ai.sound.donna</t>
         </is>
       </c>
-      <c r="C171" t="n">
+      <c r="C171" s="0" t="n">
         <v>177</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="0" t="inlineStr">
         <is>
           <t>plant identify</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" s="0" t="inlineStr">
         <is>
           <t>com.aiplant.identify.scanner.care</t>
         </is>
       </c>
-      <c r="C172" t="n">
+      <c r="C172" s="0" t="n">
         <v>179</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="0" t="inlineStr">
         <is>
           <t>ai voice change/ ai voice generator</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B173" s="0" t="inlineStr">
         <is>
           <t>io.elevenlabs.coreapp</t>
         </is>
       </c>
-      <c r="C173" t="n">
+      <c r="C173" s="0" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="0" t="inlineStr">
         <is>
           <t>photobooth camera</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B174" s="0" t="inlineStr">
         <is>
           <t>com.photobooth.camera.photo.layout.sticker.frame.collage</t>
         </is>
       </c>
-      <c r="C174" t="n">
+      <c r="C174" s="0" t="n">
         <v>181</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="0" t="inlineStr">
         <is>
           <t>pixlume - ai couple generator</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B175" s="0" t="inlineStr">
         <is>
           <t>net.pixlume.film</t>
         </is>
       </c>
-      <c r="C175" t="n">
+      <c r="C175" s="0" t="n">
         <v>182</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="0" t="inlineStr">
         <is>
           <t>diy reverse voice: sing &amp; talk</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B176" s="0" t="inlineStr">
         <is>
           <t>com.diy.ai.launcher.reverse.voice</t>
         </is>
       </c>
-      <c r="C176" t="n">
+      <c r="C176" s="0" t="n">
         <v>183</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="0" t="inlineStr">
         <is>
           <t>cat translator – human to pet</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B177" s="0" t="inlineStr">
         <is>
           <t>com.artpol.cat.translator</t>
         </is>
       </c>
-      <c r="C177" t="n">
+      <c r="C177" s="0" t="n">
         <v>184</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="0" t="inlineStr">
         <is>
           <t>pill remind</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B178" s="0" t="inlineStr">
         <is>
           <t>com.medisafe.android.client</t>
         </is>
       </c>
-      <c r="C178" t="n">
+      <c r="C178" s="0" t="n">
         <v>185</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="0" t="inlineStr">
         <is>
           <t>brainrot: screen time control</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B179" s="0" t="inlineStr">
         <is>
           <t>6744338972</t>
         </is>
       </c>
-      <c r="C179" t="n">
+      <c r="C179" s="0" t="n">
         <v>186</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="0" t="inlineStr">
         <is>
           <t>color finder and picker</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B180" s="0" t="inlineStr">
         <is>
           <t>mustafa.color_finder_and_picker</t>
         </is>
       </c>
-      <c r="C180" t="n">
+      <c r="C180" s="0" t="n">
         <v>187</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="0" t="inlineStr">
         <is>
           <t>scary prank call &amp; fake chat</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" s="0" t="inlineStr">
         <is>
           <t>com.scary.prankcall.fakechat.simulator</t>
         </is>
       </c>
-      <c r="C181" t="n">
+      <c r="C181" s="0" t="n">
         <v>188</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="0" t="inlineStr">
         <is>
           <t>voice changer</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B182" s="0" t="inlineStr">
         <is>
           <t>com.reversevoice.voicechangerapp.sound.effects</t>
         </is>
       </c>
-      <c r="C182" t="n">
+      <c r="C182" s="0" t="n">
         <v>189</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="0" t="inlineStr">
         <is>
           <t>applock pro - app lock &amp; guard</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" s="0" t="inlineStr">
         <is>
           <t>com.ibragunduz.applockpro</t>
         </is>
       </c>
-      <c r="C183" t="n">
+      <c r="C183" s="0" t="n">
         <v>190</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="0" t="inlineStr">
         <is>
           <t>recover deleted messages app</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B184" s="0" t="inlineStr">
         <is>
           <t>recover.deleted.messages.business.messagerecovery</t>
         </is>
       </c>
-      <c r="C184" t="n">
+      <c r="C184" s="0" t="n">
         <v>191</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="0" t="inlineStr">
         <is>
           <t>rezona: make memeplays</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B185" s="0" t="inlineStr">
         <is>
           <t>ai.rezona.app</t>
         </is>
       </c>
-      <c r="C185" t="n">
+      <c r="C185" s="0" t="n">
         <v>192</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="0" t="inlineStr">
         <is>
           <t>wishlist app</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B186" s="0" t="inlineStr">
         <is>
           <t>1591312803</t>
         </is>
       </c>
-      <c r="C186" t="n">
+      <c r="C186" s="0" t="n">
         <v>193</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="0" t="inlineStr">
         <is>
           <t>flirty messages &amp; pickup lines</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B187" s="0" t="inlineStr">
         <is>
           <t>pickupline.lovemessages.flirting</t>
         </is>
       </c>
-      <c r="C187" t="n">
+      <c r="C187" s="0" t="n">
         <v>194</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="0" t="inlineStr">
         <is>
           <t>emberly: ai photo generator</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B188" s="0" t="inlineStr">
         <is>
           <t>com.aicouple.photogenerator.couplephoto</t>
         </is>
       </c>
-      <c r="C188" t="n">
+      <c r="C188" s="0" t="n">
         <v>195</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="0" t="inlineStr">
         <is>
           <t>postly-status, poster &amp; videos</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B189" s="0" t="inlineStr">
         <is>
           <t>com.createmypostly.app</t>
         </is>
       </c>
-      <c r="C189" t="n">
+      <c r="C189" s="0" t="n">
         <v>196</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="0" t="inlineStr">
         <is>
           <t>moon phase match</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B190" s="0" t="inlineStr">
         <is>
           <t>com.auracam.love.vibe.test</t>
         </is>
       </c>
-      <c r="C190" t="n">
+      <c r="C190" s="0" t="n">
         <v>197</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="0" t="inlineStr">
         <is>
           <t>ai game maker</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B191" s="0" t="inlineStr">
         <is>
           <t>ai.seaverse.app</t>
         </is>
       </c>
-      <c r="C191" t="n">
+      <c r="C191" s="0" t="n">
         <v>198</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="0" t="inlineStr">
         <is>
           <t>https://apps.apple.com/vn/app/getup-smart-alarm-clock/id6761530575</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B192" s="0" t="inlineStr">
         <is>
           <t>6761530575</t>
         </is>
       </c>
-      <c r="C192" t="n">
+      <c r="C192" s="0" t="n">
         <v>199</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="0" t="inlineStr">
         <is>
           <t>fast schedule planner</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B193" s="0" t="inlineStr">
         <is>
           <t>com.schedule.taskpro.timer</t>
         </is>
       </c>
-      <c r="C193" t="n">
+      <c r="C193" s="0" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="0" t="inlineStr">
         <is>
           <t>prompt seen: ai photo prompts</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B194" s="0" t="inlineStr">
         <is>
           <t>com.promptseen.ai</t>
         </is>
       </c>
-      <c r="C194" t="n">
+      <c r="C194" s="0" t="n">
         <v>201</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="0" t="inlineStr">
         <is>
           <t>áp cảnh báo giao thông</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B195" s="0" t="inlineStr">
         <is>
           <t>com.wynauto.wyn</t>
         </is>
       </c>
-      <c r="C195" t="n">
+      <c r="C195" s="0" t="n">
         <v>202</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="0" t="inlineStr">
         <is>
           <t>mico - widget &amp; live wallpaper</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B196" s="0" t="inlineStr">
         <is>
           <t>com.sm.mico</t>
         </is>
       </c>
-      <c r="C196" t="n">
+      <c r="C196" s="0" t="n">
         <v>203</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="0" t="inlineStr">
         <is>
           <t>photoest</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B197" s="0" t="inlineStr">
         <is>
           <t>6776661427</t>
         </is>
       </c>
-      <c r="C197" t="n">
+      <c r="C197" s="0" t="n">
         <v>204</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="0" t="inlineStr">
         <is>
           <t>recovery lost photos &amp; videos</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B198" s="0" t="inlineStr">
         <is>
           <t>com.brighteasestudio.photorecovery.recoveryallfiles</t>
         </is>
       </c>
-      <c r="C198" t="n">
+      <c r="C198" s="0" t="n">
         <v>205</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="0" t="inlineStr">
         <is>
           <t>lovish ai: interactive ai chat</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B199" s="0" t="inlineStr">
         <is>
           <t>com.ninjasalary.lovish</t>
         </is>
       </c>
-      <c r="C199" t="n">
+      <c r="C199" s="0" t="n">
         <v>206</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="0" t="inlineStr">
         <is>
           <t>ai studio product</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B200" s="0" t="inlineStr">
         <is>
           <t>com.xjprhinox.pixora</t>
         </is>
       </c>
-      <c r="C200" t="n">
+      <c r="C200" s="0" t="n">
         <v>207</v>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="0" t="inlineStr">
         <is>
           <t>oslink</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B201" s="0" t="inlineStr">
         <is>
           <t>io.oslink.link</t>
         </is>
       </c>
-      <c r="C201" t="n">
+      <c r="C201" s="0" t="n">
         <v>208</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="0" t="inlineStr">
         <is>
           <t>gearup: lower lag game booster</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B202" s="0" t="inlineStr">
         <is>
           <t>com.gearup.booster</t>
         </is>
       </c>
-      <c r="C202" t="n">
+      <c r="C202" s="0" t="n">
         <v>209</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="0" t="inlineStr">
         <is>
           <t>prank sounds: haircut &amp; taser</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B203" s="0" t="inlineStr">
         <is>
           <t>com.prank.sound.airhorn.haircut.razor.clipper</t>
         </is>
       </c>
-      <c r="C203" t="n">
+      <c r="C203" s="0" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="0" t="inlineStr">
         <is>
           <t>modstune – ai car designer</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B204" s="0" t="inlineStr">
         <is>
           <t>com.mara.modstune</t>
         </is>
       </c>
-      <c r="C204" t="n">
+      <c r="C204" s="0" t="n">
         <v>211</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="0" t="inlineStr">
         <is>
           <t>caller id &amp; spam call blocker</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B205" s="0" t="inlineStr">
         <is>
           <t>app.smart.trusted.callerid.smsblocker</t>
         </is>
       </c>
-      <c r="C205" t="n">
+      <c r="C205" s="0" t="n">
         <v>212</v>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="0" t="inlineStr">
         <is>
           <t>gps photo stamp map camera</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B206" s="0" t="inlineStr">
         <is>
           <t>com.blazingappstudio.gps_photo</t>
         </is>
       </c>
-      <c r="C206" t="n">
+      <c r="C206" s="0" t="n">
         <v>213</v>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="A207" s="0" t="inlineStr">
         <is>
           <t>ranking filter: fun challenge</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B207" s="0" t="inlineStr">
         <is>
           <t>com.godhitech.rankingchallenge.funfilter</t>
         </is>
       </c>
-      <c r="C207" t="n">
+      <c r="C207" s="0" t="n">
         <v>214</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="A208" s="0" t="inlineStr">
         <is>
           <t>elevenlabs: ai voice generator</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B208" s="0" t="inlineStr">
         <is>
           <t>io.elevenlabs.coreapp</t>
         </is>
       </c>
-      <c r="C208" t="n">
+      <c r="C208" s="0" t="n">
         <v>215</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="A209" s="0" t="inlineStr">
         <is>
           <t>palmistry ai: destiny - zodiac</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B209" s="0" t="inlineStr">
         <is>
           <t>com.ego.scanpalmistry.palm.zodiac.horoscope.ai</t>
         </is>
       </c>
-      <c r="C209" t="n">
+      <c r="C209" s="0" t="n">
         <v>216</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="A210" s="0" t="inlineStr">
         <is>
           <t>broken screen prank &amp; sound</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B210" s="0" t="inlineStr">
         <is>
           <t>brokenscreenprank.fakephonescreen.funny.prank.brokenscreen</t>
         </is>
       </c>
-      <c r="C210" t="n">
+      <c r="C210" s="0" t="n">
         <v>217</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
+      <c r="A211" s="0" t="inlineStr">
         <is>
           <t>novelbite - stories &amp; novels</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B211" s="0" t="inlineStr">
         <is>
           <t>com.novelbite.novel</t>
         </is>
       </c>
-      <c r="C211" t="n">
+      <c r="C211" s="0" t="n">
         <v>218</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
+      <c r="A212" s="0" t="inlineStr">
         <is>
           <t>unseen chat &amp; track: sneakly</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B212" s="0" t="inlineStr">
         <is>
           <t>com.sneakly.unseen.chat.app</t>
         </is>
       </c>
-      <c r="C212" t="n">
+      <c r="C212" s="0" t="n">
         <v>219</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="0" t="inlineStr">
         <is>
           <t>sherlock : face search ai</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B213" s="0" t="inlineStr">
         <is>
           <t>com.ai.facesearch.photo.app</t>
         </is>
       </c>
-      <c r="C213" t="n">
+      <c r="C213" s="0" t="n">
         <v>220</v>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="A214" s="0" t="inlineStr">
         <is>
           <t>friendkit</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B214" s="0" t="inlineStr">
         <is>
           <t>com.friendkit.messenger_message_manager</t>
         </is>
       </c>
-      <c r="C214" t="n">
+      <c r="C214" s="0" t="n">
         <v>221</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="0" t="inlineStr">
         <is>
           <t>ai family maker</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" s="0" t="inlineStr">
         <is>
           <t>io.photora.mood</t>
         </is>
       </c>
-      <c r="C215" t="n">
+      <c r="C215" s="0" t="n">
         <v>222</v>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="0" t="inlineStr">
         <is>
           <t>digital camera hd - 4k camera</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B216" s="0" t="inlineStr">
         <is>
           <t>com.hd.camera.professional.photo.tool</t>
         </is>
       </c>
-      <c r="C216" t="n">
+      <c r="C216" s="0" t="n">
         <v>223</v>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="0" t="inlineStr">
         <is>
           <t>ar character: viral fun filter</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B217" s="0" t="inlineStr">
         <is>
           <t>co.ar.dogy.trendingfilter</t>
         </is>
       </c>
-      <c r="C217" t="n">
+      <c r="C217" s="0" t="n">
         <v>224</v>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="0" t="inlineStr">
         <is>
           <t>private photos</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" s="0" t="inlineStr">
         <is>
           <t>com.applock.photovault.hiddenapps</t>
         </is>
       </c>
-      <c r="C218" t="n">
+      <c r="C218" s="0" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="0" t="inlineStr">
         <is>
           <t>delete ex photos</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B219" s="0" t="inlineStr">
         <is>
           <t>6751822284</t>
         </is>
       </c>
-      <c r="C219" t="n">
+      <c r="C219" s="0" t="n">
         <v>226</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="0" t="inlineStr">
         <is>
           <t>origami world: learn &amp; play</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B220" s="0" t="inlineStr">
         <is>
           <t>com.origami.paper.folding.craft.guide.relax.learn.magic</t>
         </is>
       </c>
-      <c r="C220" t="n">
+      <c r="C220" s="0" t="n">
         <v>227</v>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="0" t="inlineStr">
         <is>
           <t>all document reader: pdf tools</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B221" s="0" t="inlineStr">
         <is>
           <t>com.filemanager.document.viewer.reader.alldoc.pdfeditor</t>
         </is>
       </c>
-      <c r="C221" t="n">
+      <c r="C221" s="0" t="n">
         <v>228</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="0" t="inlineStr">
         <is>
           <t>iptv player: hd online tv</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B222" s="0" t="inlineStr">
         <is>
           <t>com.iptvplayer.iptv.app</t>
         </is>
       </c>
-      <c r="C222" t="n">
+      <c r="C222" s="0" t="n">
         <v>229</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="0" t="inlineStr">
         <is>
           <t>nova vpn</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B223" s="0" t="inlineStr">
         <is>
           <t>com.novaproxy.mastervpn.besservice</t>
         </is>
       </c>
-      <c r="C223" t="n">
+      <c r="C223" s="0" t="n">
         <v>230</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="0" t="inlineStr">
         <is>
           <t>tap challenge - viral filter</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B224" s="0" t="inlineStr">
         <is>
           <t>com.filter.challenge.viral.funny.fyp.tap.mini.games.trends</t>
         </is>
       </c>
-      <c r="C224" t="n">
+      <c r="C224" s="0" t="n">
         <v>231</v>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="A225" s="0" t="inlineStr">
         <is>
           <t>photo blur &amp; mosaic effects</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B225" s="0" t="inlineStr">
         <is>
           <t>com.stellaxia.mosaicplus</t>
         </is>
       </c>
-      <c r="C225" t="n">
+      <c r="C225" s="0" t="n">
         <v>232</v>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="A226" s="0" t="inlineStr">
         <is>
           <t>lockscreen calendar maker</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B226" s="0" t="inlineStr">
         <is>
           <t>com.vimask.lockscreencalendarmaker</t>
         </is>
       </c>
-      <c r="C226" t="n">
+      <c r="C226" s="0" t="n">
         <v>233</v>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="A227" s="0" t="inlineStr">
         <is>
           <t>photobooth cam: frame &amp; filter</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B227" s="0" t="inlineStr">
         <is>
           <t>com.photobooth.camera.photo.layout.sticker.frame.collage</t>
         </is>
       </c>
-      <c r="C227" t="n">
+      <c r="C227" s="0" t="n">
         <v>234</v>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="A228" s="0" t="inlineStr">
         <is>
           <t>dailybean: simplest journal</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B228" s="0" t="inlineStr">
         <is>
           <t>com.bluesignum.bluediary</t>
         </is>
       </c>
-      <c r="C228" t="n">
+      <c r="C228" s="0" t="n">
         <v>235</v>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
+      <c r="A229" s="0" t="inlineStr">
         <is>
           <t>dokichat - romantic ai chats</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B229" s="0" t="inlineStr">
         <is>
           <t>app.doki.dokichat</t>
         </is>
       </c>
-      <c r="C229" t="n">
+      <c r="C229" s="0" t="n">
         <v>236</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="0" t="inlineStr">
         <is>
           <t>weathersight - live forecast</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" s="0" t="inlineStr">
         <is>
           <t>com.sight.cleken.weather</t>
         </is>
       </c>
-      <c r="C230" t="n">
+      <c r="C230" s="0" t="n">
         <v>237</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="A231" s="0" t="inlineStr">
         <is>
           <t>volume control home</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B231" s="0" t="inlineStr">
         <is>
           <t>com.eet.volume.launcher</t>
         </is>
       </c>
-      <c r="C231" t="n">
+      <c r="C231" s="0" t="n">
         <v>238</v>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="A232" s="0" t="inlineStr">
         <is>
           <t>battery info - health monitor</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B232" s="0" t="inlineStr">
         <is>
           <t>com.batteryinfoo.batteryinfo</t>
         </is>
       </c>
-      <c r="C232" t="n">
+      <c r="C232" s="0" t="n">
         <v>239</v>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
+      <c r="A233" s="0" t="inlineStr">
         <is>
           <t>mp3 video converter</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="0" t="inlineStr">
         <is>
           <t>com.videotomp3.mp3cutter.mp3merger</t>
         </is>
       </c>
-      <c r="C233" t="n">
+      <c r="C233" s="0" t="n">
         <v>240</v>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="A234" s="0" t="inlineStr">
         <is>
           <t>tiktok repost remove</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="0" t="inlineStr">
         <is>
           <t>com.datatraces.cleartok</t>
         </is>
       </c>
-      <c r="C234" t="n">
+      <c r="C234" s="0" t="n">
         <v>241</v>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="0" t="inlineStr">
         <is>
           <t>tutorme: ai english learning</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="0" t="inlineStr">
         <is>
           <t>tutorme.learning.english.ai</t>
         </is>
       </c>
-      <c r="C235" t="n">
+      <c r="C235" s="0" t="n">
         <v>242</v>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="0" t="inlineStr">
         <is>
           <t>camera detector hidden</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="0" t="inlineStr">
         <is>
           <t>com.camera.detector.hiddencheck.privacyscan</t>
         </is>
       </c>
-      <c r="C236" t="n">
+      <c r="C236" s="0" t="n">
         <v>243</v>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="0" t="inlineStr">
         <is>
           <t>aimpro - custom crosshair</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="0" t="inlineStr">
         <is>
           <t>com.customcrosshair.aimpro</t>
         </is>
       </c>
-      <c r="C237" t="n">
+      <c r="C237" s="0" t="n">
         <v>244</v>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="A238" s="0" t="inlineStr">
         <is>
           <t>diy reverse voice: sing &amp; talk</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" s="0" t="inlineStr">
         <is>
           <t>com.diy.ai.launcher.reverse.voice</t>
         </is>
       </c>
-      <c r="C238" t="n">
+      <c r="C238" s="0" t="n">
         <v>245</v>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="0" t="inlineStr">
         <is>
           <t>timeline visual gg map</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" s="0" t="inlineStr">
         <is>
           <t>com.seltra.apptimeline</t>
         </is>
       </c>
-      <c r="C239" t="n">
+      <c r="C239" s="0" t="n">
         <v>246</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="0" t="inlineStr">
         <is>
           <t>sanpou voice meme let it go</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B240" s="0" t="inlineStr">
         <is>
           <t>6749672561</t>
         </is>
       </c>
-      <c r="C240" t="n">
+      <c r="C240" s="0" t="n">
         <v>247</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="0" t="inlineStr">
         <is>
           <t>hearstory: short audio stories</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B241" s="0" t="inlineStr">
         <is>
           <t>com.readbook.bookstore.audiobooks</t>
         </is>
       </c>
-      <c r="C241" t="n">
+      <c r="C241" s="0" t="n">
         <v>248</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="0" t="inlineStr">
         <is>
           <t>ar ruler: tape measure tools</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B242" s="0" t="inlineStr">
         <is>
           <t>com.starnest.arruler.ruler</t>
         </is>
       </c>
-      <c r="C242" t="n">
+      <c r="C242" s="0" t="n">
         <v>249</v>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="0" t="inlineStr">
         <is>
           <t>vokey - voice screen lock</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B243" s="0" t="inlineStr">
         <is>
           <t>com.capslock.vokey</t>
         </is>
       </c>
-      <c r="C243" t="n">
+      <c r="C243" s="0" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="0" t="inlineStr">
         <is>
           <t>piano keyboard: play &amp; learn</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B244" s="0" t="inlineStr">
         <is>
           <t>com.learn.play.keyboard.piano.songs</t>
         </is>
       </c>
-      <c r="C244" t="n">
+      <c r="C244" s="0" t="n">
         <v>251</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="0" t="inlineStr">
         <is>
           <t>ace scanner - pdf scanner app</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B245" s="0" t="inlineStr">
         <is>
           <t>free.scanner.scan.pdf.cam.camscanner</t>
         </is>
       </c>
-      <c r="C245" t="n">
+      <c r="C245" s="0" t="n">
         <v>252</v>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="0" t="inlineStr">
         <is>
           <t>mentalyze・ai for mental health</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B246" s="0" t="inlineStr">
         <is>
           <t>ai.mentalyze</t>
         </is>
       </c>
-      <c r="C246" t="n">
+      <c r="C246" s="0" t="n">
         <v>253</v>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="A247" s="0" t="inlineStr">
         <is>
           <t>alarm clock - challenge alarm</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B247" s="0" t="inlineStr">
         <is>
           <t>com.clock.alarmclock.loudalarm.alarm</t>
         </is>
       </c>
-      <c r="C247" t="n">
+      <c r="C247" s="0" t="n">
         <v>254</v>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="0" t="inlineStr">
         <is>
           <t>speedtest by ookla</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B248" s="0" t="inlineStr">
         <is>
           <t>com.playtube.vancedtube.tubevanced.adsfree</t>
         </is>
       </c>
-      <c r="C248" t="n">
+      <c r="C248" s="0" t="n">
         <v>255</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="0" t="inlineStr">
         <is>
           <t>water tracker: water reminder</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B249" s="0" t="inlineStr">
         <is>
           <t>org.zwanoo.android.speedtest</t>
         </is>
       </c>
-      <c r="C249" t="n">
+      <c r="C249" s="0" t="n">
         <v>256</v>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="0" t="inlineStr">
         <is>
           <t>anime ai</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B250" s="0" t="inlineStr">
         <is>
           <t>com.ai.anime.photo.create</t>
         </is>
       </c>
-      <c r="C250" t="n">
+      <c r="C250" s="0" t="n">
         <v>257</v>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="0" t="inlineStr">
         <is>
           <t>timecue – reminders &amp; alerts</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B251" s="0" t="inlineStr">
         <is>
           <t>com.reminder.alert.timecue</t>
         </is>
       </c>
-      <c r="C251" t="n">
+      <c r="C251" s="0" t="n">
         <v>258</v>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="0" t="inlineStr">
         <is>
           <t>pure tuber: video &amp; mp3 player</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B252" s="0" t="inlineStr">
         <is>
           <t>free.tube.premium.advanced.tuber</t>
         </is>
       </c>
-      <c r="C252" t="n">
+      <c r="C252" s="0" t="n">
         <v>259</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="0" t="inlineStr">
         <is>
           <t>musa: period &amp; self-care pet</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="0" t="inlineStr">
         <is>
           <t>com.musa.musa</t>
         </is>
       </c>
-      <c r="C253" t="n">
+      <c r="C253" s="0" t="n">
         <v>260</v>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
+      <c r="A254" s="0" t="inlineStr">
         <is>
           <t>storytoon: manhwa, manga comic</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="0" t="inlineStr">
         <is>
           <t>com.shop.pocketreading.appmanga</t>
         </is>
       </c>
-      <c r="C254" t="n">
+      <c r="C254" s="0" t="n">
         <v>261</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="0" t="inlineStr">
         <is>
           <t>photo recover ultra</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="0" t="inlineStr">
         <is>
           <t>filerecovery.photosrecovery.allrecovery</t>
         </is>
       </c>
-      <c r="C255" t="n">
+      <c r="C255" s="0" t="n">
         <v>262</v>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="0" t="inlineStr">
         <is>
           <t>sleep sounds - smart alarm</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B256" s="0" t="inlineStr">
         <is>
           <t>com.calm.android</t>
         </is>
       </c>
-      <c r="C256" t="n">
+      <c r="C256" s="0" t="n">
         <v>263</v>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="0" t="inlineStr">
         <is>
           <t>lagzero: gaming tools</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="0" t="inlineStr">
         <is>
           <t>com.lagzero.game.fps.booster.optimizer</t>
         </is>
       </c>
-      <c r="C257" t="n">
+      <c r="C257" s="0" t="n">
         <v>264</v>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="0" t="inlineStr">
         <is>
           <t>superlabor - daily attendance</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B258" s="0" t="inlineStr">
         <is>
           <t>app.superlabor</t>
         </is>
       </c>
-      <c r="C258" t="n">
+      <c r="C258" s="0" t="n">
         <v>265</v>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="0" t="inlineStr">
         <is>
           <t>hand magic</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B259" s="0" t="inlineStr">
         <is>
           <t>com.teh.software.hand.magic.control</t>
         </is>
       </c>
-      <c r="C259" t="n">
+      <c r="C259" s="0" t="n">
         <v>266</v>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
+      <c r="A260" s="0" t="inlineStr">
         <is>
           <t>fazee - funny face filter</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B260" s="0" t="inlineStr">
         <is>
           <t>com.face.filters.funny.filter.timewarp.camera.prank</t>
         </is>
       </c>
-      <c r="C260" t="n">
+      <c r="C260" s="0" t="n">
         <v>269</v>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="A261" s="0" t="inlineStr">
         <is>
           <t>langla: ai language tutor</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B261" s="0" t="inlineStr">
         <is>
           <t>aitutor.ailanguagelearn.ailearning</t>
         </is>
       </c>
-      <c r="C261" t="n">
+      <c r="C261" s="0" t="n">
         <v>270</v>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="0" t="inlineStr">
         <is>
           <t>wedraw: lockscreen drawing</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B262" s="0" t="inlineStr">
         <is>
           <t>lock.screen.drawing.lockscreen.draw.together.couple.widget</t>
         </is>
       </c>
-      <c r="C262" t="n">
+      <c r="C262" s="0" t="n">
         <v>271</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
+      <c r="A263" s="0" t="inlineStr">
         <is>
           <t>mapsy : live earth map</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B263" s="0" t="inlineStr">
         <is>
           <t>com.live.streetview.livecam.maps.earth</t>
         </is>
       </c>
-      <c r="C263" t="n">
+      <c r="C263" s="0" t="n">
         <v>272</v>
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
+      <c r="A264" s="0" t="inlineStr">
         <is>
           <t>ai face swap</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B264" s="0" t="inlineStr">
         <is>
           <t>com.animateimage.create.trending.artmaker</t>
         </is>
       </c>
-      <c r="C264" t="n">
+      <c r="C264" s="0" t="n">
         <v>273</v>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
+      <c r="A265" s="0" t="inlineStr">
         <is>
           <t>food health scanner</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B265" s="0" t="inlineStr">
         <is>
           <t>com.getscanly.app</t>
         </is>
       </c>
-      <c r="C265" t="n">
+      <c r="C265" s="0" t="n">
         <v>274</v>
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
+      <c r="A266" s="0" t="inlineStr">
         <is>
           <t>qibla compass</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B266" s="0" t="inlineStr">
         <is>
           <t>com.qibla.compass.qiblafinder.direction</t>
         </is>
       </c>
-      <c r="C266" t="n">
+      <c r="C266" s="0" t="n">
         <v>275</v>
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
+      <c r="A267" s="0" t="inlineStr">
         <is>
           <t>baby &amp; pregnancy tracker app</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B267" s="0" t="inlineStr">
         <is>
           <t>com.bellybloom.pregnancy.tracker</t>
         </is>
       </c>
-      <c r="C267" t="n">
+      <c r="C267" s="0" t="n">
         <v>276</v>
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
+      <c r="A268" s="0" t="inlineStr">
         <is>
           <t>blood sugar &amp; pressure tracker</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B268" s="0" t="inlineStr">
         <is>
           <t>com.bp.blood.sugar.pressure.tracker.app</t>
         </is>
       </c>
-      <c r="C268" t="n">
+      <c r="C268" s="0" t="n">
         <v>277</v>
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
+      <c r="A269" s="0" t="inlineStr">
         <is>
           <t>daily zodiac &amp; tarot spread</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B269" s="0" t="inlineStr">
         <is>
           <t>com.aitarot.labrinthstyle.cosmic.board</t>
         </is>
       </c>
-      <c r="C269" t="n">
+      <c r="C269" s="0" t="n">
         <v>278</v>
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
+      <c r="A270" s="0" t="inlineStr">
         <is>
           <t>outfitly – ai outfit rating</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B270" s="0" t="inlineStr">
         <is>
           <t>com.outfitai.outfitly</t>
         </is>
       </c>
-      <c r="C270" t="n">
+      <c r="C270" s="0" t="n">
         <v>279</v>
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
+      <c r="A271" s="0" t="inlineStr">
         <is>
           <t>nodi: lofi music focus timer</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B271" s="0" t="inlineStr">
         <is>
           <t>com.daarbit.nodistractions</t>
         </is>
       </c>
-      <c r="C271" t="n">
+      <c r="C271" s="0" t="n">
         <v>280</v>
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
+      <c r="A272" s="0" t="inlineStr">
         <is>
           <t>pregnancy tracker: baby growth</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B272" s="0" t="inlineStr">
         <is>
           <t>com.evtool.babygrowth.pregnancytracker</t>
         </is>
       </c>
-      <c r="C272" t="n">
+      <c r="C272" s="0" t="n">
         <v>281</v>
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
+      <c r="A273" s="0" t="inlineStr">
         <is>
           <t>crochet knit yarn: row counter</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B273" s="0" t="inlineStr">
         <is>
           <t>com.moniq.crochet.knit.rowcounter</t>
         </is>
       </c>
-      <c r="C273" t="n">
+      <c r="C273" s="0" t="n">
         <v>282</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
+      <c r="A274" s="0" t="inlineStr">
         <is>
           <t>ngl: ask me anything</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B274" s="0" t="inlineStr">
         <is>
           <t>com.nglreactnative</t>
         </is>
       </c>
-      <c r="C274" t="n">
+      <c r="C274" s="0" t="n">
         <v>284</v>
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
+      <c r="A275" s="0" t="inlineStr">
         <is>
           <t>diy wallpaper craft</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B275" s="0" t="inlineStr">
         <is>
           <t>com.yoursify.diy.wallpaper.collage.craft.cutout.photo</t>
         </is>
       </c>
-      <c r="C275" t="n">
+      <c r="C275" s="0" t="n">
         <v>285</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
+      <c r="A276" s="0" t="inlineStr">
         <is>
           <t>volume control home</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B276" s="0" t="inlineStr">
         <is>
           <t>com.eet.volume.launcher</t>
         </is>
       </c>
-      <c r="C276" t="n">
+      <c r="C276" s="0" t="n">
         <v>286</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
+      <c r="A277" s="0" t="inlineStr">
         <is>
           <t>time warp scan - face scanner</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B277" s="0" t="inlineStr">
         <is>
           <t>com.timewarp.scan.bluelinefiltertiktok.free</t>
         </is>
       </c>
-      <c r="C277" t="n">
+      <c r="C277" s="0" t="n">
         <v>287</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
+      <c r="A278" s="0" t="inlineStr">
         <is>
           <t>color phone: call screen theme</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B278" s="0" t="inlineStr">
         <is>
           <t>com.colorphone.callscreen.wallpaper.callthemes</t>
         </is>
       </c>
-      <c r="C278" t="n">
+      <c r="C278" s="0" t="n">
         <v>288</v>
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
+      <c r="A279" s="0" t="inlineStr">
         <is>
           <t>pregnancy test app: test check</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B279" s="0" t="inlineStr">
         <is>
           <t>baby.pregnancy.tracker.app</t>
         </is>
       </c>
-      <c r="C279" t="n">
+      <c r="C279" s="0" t="n">
         <v>289</v>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
+      <c r="A280" s="0" t="inlineStr">
         <is>
           <t>check-chat - last seen</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B280" s="0" t="inlineStr">
         <is>
           <t>check.chat.com.app</t>
         </is>
       </c>
-      <c r="C280" t="n">
+      <c r="C280" s="0" t="n">
         <v>290</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
+      <c r="A281" s="0" t="inlineStr">
         <is>
           <t>2026-11-09 00:00:00</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B281" s="0" t="inlineStr">
         <is>
           <t>com.photo.sticker.stickermaker</t>
         </is>
       </c>
-      <c r="C281" t="n">
+      <c r="C281" s="0" t="n">
         <v>291</v>
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
+      <c r="A282" s="0" t="inlineStr">
         <is>
           <t>origami guide: learn &amp; fold</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr"/>
-      <c r="C282" t="n">
+      <c r="B282" s="0" t="inlineStr"/>
+      <c r="C282" s="0" t="n">
         <v>292</v>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
+      <c r="A283" s="0" t="inlineStr">
         <is>
           <t>fashion design clothes: sketch</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr"/>
-      <c r="C283" t="n">
+      <c r="B283" s="0" t="inlineStr"/>
+      <c r="C283" s="0" t="n">
         <v>293</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
+      <c r="A284" s="0" t="inlineStr">
         <is>
           <t>speech path</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B284" s="0" t="inlineStr">
         <is>
           <t>6745437939</t>
         </is>
       </c>
-      <c r="C284" t="n">
+      <c r="C284" s="0" t="n">
         <v>294</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
+      <c r="A285" s="0" t="inlineStr">
         <is>
           <t>lumus: psychic &amp; tarot reading</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B285" s="0" t="inlineStr">
         <is>
           <t>com.astrology.psychics</t>
         </is>
       </c>
-      <c r="C285" t="n">
+      <c r="C285" s="0" t="n">
         <v>295</v>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
+      <c r="A286" s="0" t="inlineStr">
         <is>
           <t>lookup number : find caller</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B286" s="0" t="inlineStr">
         <is>
           <t>com.number.lookup.app.caller.id</t>
         </is>
       </c>
-      <c r="C286" t="n">
+      <c r="C286" s="0" t="n">
         <v>296</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
+      <c r="A287" s="0" t="inlineStr">
         <is>
           <t>mimic art: ai photo generator</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B287" s="0" t="inlineStr">
         <is>
           <t>com.mimic.image.aiphotogenerator</t>
         </is>
       </c>
-      <c r="C287" t="n">
+      <c r="C287" s="0" t="n">
         <v>297</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
+      <c r="A288" s="0" t="inlineStr">
         <is>
           <t>ai collage maker &amp; photo frame</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B288" s="0" t="inlineStr">
         <is>
           <t>com.photocollage.collagemaker.photoeditor.photoframe</t>
         </is>
       </c>
-      <c r="C288" t="n">
+      <c r="C288" s="0" t="n">
         <v>298</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
+      <c r="A289" s="0" t="inlineStr">
         <is>
           <t>art mate together: how to draw</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B289" s="0" t="inlineStr">
         <is>
           <t>com.artmate.drawing.together.howtodraw</t>
         </is>
       </c>
-      <c r="C289" t="n">
+      <c r="C289" s="0" t="n">
         <v>299</v>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
+      <c r="A290" s="0" t="inlineStr">
         <is>
           <t>lie detector launcher</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B290" s="0" t="inlineStr">
         <is>
           <t>com.lie.detector.prank.tool</t>
         </is>
       </c>
-      <c r="C290" t="n">
+      <c r="C290" s="0" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
+      <c r="A291" s="0" t="inlineStr">
         <is>
           <t>voice translator: speak &amp; chat</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
+      <c r="B291" s="0" t="inlineStr">
         <is>
           <t>com.translate.language.multi.translator</t>
         </is>
       </c>
-      <c r="C291" t="n">
+      <c r="C291" s="0" t="n">
         <v>301</v>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
+      <c r="A292" s="0" t="inlineStr">
         <is>
           <t>outfityz: ai outfit swap</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
+      <c r="B292" s="0" t="inlineStr">
         <is>
           <t>com.fumaomao.outfityz</t>
         </is>
       </c>
-      <c r="C292" t="n">
+      <c r="C292" s="0" t="n">
         <v>302</v>
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
+      <c r="A293" s="0" t="inlineStr">
         <is>
           <t>pet on screen - shimeji kawai</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
+      <c r="B293" s="0" t="inlineStr">
         <is>
           <t>com.shimeji.kawaii.desktop.screen.pet</t>
         </is>
       </c>
-      <c r="C293" t="n">
+      <c r="C293" s="0" t="n">
         <v>303</v>
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
+      <c r="A294" s="0" t="inlineStr">
         <is>
           <t>led banner: edge lighting</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
+      <c r="B294" s="0" t="inlineStr">
         <is>
           <t>com.az.ledbanner.text.scroller</t>
         </is>
       </c>
-      <c r="C294" t="n">
+      <c r="C294" s="0" t="n">
         <v>304</v>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
+      <c r="A295" s="0" t="inlineStr">
         <is>
           <t>heribase: ai coin identifier</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
+      <c r="B295" s="0" t="inlineStr">
         <is>
           <t>com.weipaitang.coin</t>
         </is>
       </c>
-      <c r="C295" t="n">
+      <c r="C295" s="0" t="n">
         <v>305</v>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
+      <c r="A296" s="0" t="inlineStr">
         <is>
           <t>tcg trading card mart owner</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B296" s="0" t="inlineStr">
         <is>
           <t>com.blingames.managetcgcardmartsimulator</t>
         </is>
       </c>
-      <c r="C296" t="n">
+      <c r="C296" s="0" t="n">
         <v>306</v>
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
+      <c r="A297" s="0" t="inlineStr">
         <is>
           <t>screenplus</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
+      <c r="B297" s="0" t="inlineStr">
         <is>
           <t>com.app.screenplus</t>
         </is>
       </c>
-      <c r="C297" t="n">
+      <c r="C297" s="0" t="n">
         <v>307</v>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
+      <c r="A298" s="0" t="inlineStr">
         <is>
           <t>roomai: ai interior design</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B298" s="0" t="inlineStr">
         <is>
           <t>com.omgbros.interiorai.ai</t>
         </is>
       </c>
-      <c r="C298" t="n">
+      <c r="C298" s="0" t="n">
         <v>308</v>
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
+      <c r="A299" s="0" t="inlineStr">
         <is>
           <t>seokgamoney: buddha luck</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
+      <c r="B299" s="0" t="inlineStr">
         <is>
           <t>kim.seokgamoney.app</t>
         </is>
       </c>
-      <c r="C299" t="n">
+      <c r="C299" s="0" t="n">
         <v>309</v>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
+      <c r="A300" s="0" t="inlineStr">
         <is>
           <t>beautix - ai hair changer</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B300" s="0" t="inlineStr">
         <is>
           <t>life.growly.beautix</t>
         </is>
       </c>
-      <c r="C300" t="n">
+      <c r="C300" s="0" t="n">
         <v>310</v>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
+      <c r="A301" s="0" t="inlineStr">
         <is>
           <t>ai voice note-ai note summary</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B301" s="0" t="inlineStr">
         <is>
           <t>com.ezt.note.ainote.app</t>
         </is>
       </c>
-      <c r="C301" t="n">
+      <c r="C301" s="0" t="n">
         <v>312</v>
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
+      <c r="A302" s="0" t="inlineStr">
         <is>
           <t>fits – outfit planner &amp; closet</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B302" s="0" t="inlineStr">
         <is>
           <t>de.lhenne.fits</t>
         </is>
       </c>
-      <c r="C302" t="n">
+      <c r="C302" s="0" t="n">
         <v>313</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
+      <c r="A303" s="0" t="inlineStr">
         <is>
           <t>muslim times &amp; qibla direction</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr"/>
-      <c r="C303" t="n">
+      <c r="B303" s="0" t="inlineStr"/>
+      <c r="C303" s="0" t="n">
         <v>314</v>
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
+      <c r="A304" s="0" t="inlineStr">
         <is>
           <t>genk: micro learning &amp; topik</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr"/>
-      <c r="C304" t="n">
+      <c r="B304" s="0" t="inlineStr"/>
+      <c r="C304" s="0" t="n">
         <v>315</v>
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
+      <c r="A305" s="0" t="inlineStr">
         <is>
           <t>live photo camera:motion photo</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr"/>
-      <c r="C305" t="n">
+      <c r="B305" s="0" t="inlineStr"/>
+      <c r="C305" s="0" t="n">
         <v>316</v>
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
+      <c r="A306" s="0" t="inlineStr">
         <is>
           <t>lavo - meet new people</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr"/>
-      <c r="C306" t="n">
+      <c r="B306" s="0" t="inlineStr"/>
+      <c r="C306" s="0" t="n">
         <v>317</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
+      <c r="A307" s="0" t="inlineStr">
         <is>
           <t>datanest-recovery assistant</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
+      <c r="B307" s="0" t="inlineStr">
         <is>
           <t>com.virelma.novaryn.datanest</t>
         </is>
       </c>
-      <c r="C307" t="n">
+      <c r="C307" s="0" t="n">
         <v>318</v>
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
+      <c r="A308" s="0" t="inlineStr">
         <is>
           <t>chair workout at home</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr"/>
-      <c r="C308" t="n">
+      <c r="B308" s="0" t="inlineStr"/>
+      <c r="C308" s="0" t="n">
         <v>320</v>
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
+      <c r="A309" s="0" t="inlineStr">
         <is>
           <t>photobooth cam: frame &amp; filter</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr"/>
-      <c r="C309" t="n">
+      <c r="B309" s="0" t="inlineStr"/>
+      <c r="C309" s="0" t="n">
         <v>321</v>
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
+      <c r="A310" s="0" t="inlineStr">
         <is>
           <t>my diary – daily journal</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B310" s="0" t="inlineStr">
         <is>
           <t>com.highsecure.mydiary</t>
         </is>
       </c>
-      <c r="C310" t="n">
+      <c r="C310" s="0" t="n">
         <v>322</v>
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
+      <c r="A311" s="0" t="inlineStr">
         <is>
           <t>interactive immersive: warm up</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
+      <c r="B311" s="0" t="inlineStr">
         <is>
           <t>com.interactive.immersive.warmup</t>
         </is>
       </c>
-      <c r="C311" t="n">
+      <c r="C311" s="0" t="n">
         <v>323</v>
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
+      <c r="A312" s="0" t="inlineStr">
         <is>
           <t>ai seduce</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
+      <c r="B312" s="0" t="inlineStr">
         <is>
           <t>com.aiseduce.job.frames</t>
         </is>
       </c>
-      <c r="C312" t="n">
+      <c r="C312" s="0" t="n">
         <v>324</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
+      <c r="A313" s="0" t="inlineStr">
         <is>
           <t>ai repair assistant</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B313" s="0" t="inlineStr">
         <is>
           <t>com.repairassistant.aifix.diy</t>
         </is>
       </c>
-      <c r="C313" t="n">
+      <c r="C313" s="0" t="n">
         <v>325</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr">
+      <c r="A314" s="0" t="inlineStr">
         <is>
           <t>amora - ai character roleplay</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
+      <c r="B314" s="0" t="inlineStr">
         <is>
           <t>ai.starvia.friendi</t>
         </is>
       </c>
-      <c r="C314" t="n">
+      <c r="C314" s="0" t="n">
         <v>326</v>
       </c>
     </row>
@@ -56624,6 +56639,586 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" style="97" min="1" max="1"/>
+    <col width="26" customWidth="1" style="97" min="2" max="2"/>
+    <col width="34" customWidth="1" style="97" min="3" max="3"/>
+    <col width="20" customWidth="1" style="97" min="4" max="4"/>
+    <col width="22" customWidth="1" style="97" min="5" max="5"/>
+    <col width="10" customWidth="1" style="97" min="6" max="6"/>
+    <col width="12" customWidth="1" style="97" min="7" max="7"/>
+    <col width="12" customWidth="1" style="97" min="8" max="8"/>
+    <col width="10" customWidth="1" style="97" min="9" max="9"/>
+    <col width="26" customWidth="1" style="97" min="10" max="10"/>
+    <col width="40" customWidth="1" style="97" min="11" max="11"/>
+    <col width="46" customWidth="1" style="97" min="12" max="12"/>
+    <col width="46" customWidth="1" style="97" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="107" t="inlineStr">
+        <is>
+          <t>APP MỚI – ĐỢT 2: chưa có trong sheet, ra mắt ≤ 1 năm, ≥ 1K install/ngày (khác đợt 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="108" t="inlineStr">
+        <is>
+          <t>Số liệu từ AppBrain (lượt tải 30 ngày gần nhất, tra ngày 01/10/2026). Install/ngày = lượt tải 30 ngày ÷ 30. Đã kiểm tra tên &amp; package không có trong file. Nên xác nhận lại trên AppstoreSpy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="110" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="110" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="C4" s="110" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D4" s="110" t="inlineStr">
+        <is>
+          <t>Nhà phát triển</t>
+        </is>
+      </c>
+      <c r="E4" s="110" t="inlineStr">
+        <is>
+          <t>Ngách</t>
+        </is>
+      </c>
+      <c r="F4" s="110" t="inlineStr">
+        <is>
+          <t>Ra mắt</t>
+        </is>
+      </c>
+      <c r="G4" s="110" t="inlineStr">
+        <is>
+          <t>Tải 30 ngày</t>
+        </is>
+      </c>
+      <c r="H4" s="110" t="inlineStr">
+        <is>
+          <t>Install/ngày</t>
+        </is>
+      </c>
+      <c r="I4" s="110" t="inlineStr">
+        <is>
+          <t>Tổng tải</t>
+        </is>
+      </c>
+      <c r="J4" s="110" t="inlineStr">
+        <is>
+          <t>Ngách gần nhất trong file</t>
+        </is>
+      </c>
+      <c r="K4" s="110" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="L4" s="110" t="inlineStr">
+        <is>
+          <t>Link Google Play</t>
+        </is>
+      </c>
+      <c r="M4" s="110" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="112" t="inlineStr">
+        <is>
+          <t>Movies Drama &amp; TV series: Info</t>
+        </is>
+      </c>
+      <c r="C5" s="112" t="inlineStr">
+        <is>
+          <t>infoguide.movies.trailers.dramas.tvshows.webseries</t>
+        </is>
+      </c>
+      <c r="D5" s="112" t="inlineStr">
+        <is>
+          <t>Global Media Studio</t>
+        </is>
+      </c>
+      <c r="E5" s="112" t="inlineStr">
+        <is>
+          <t>Thông tin phim / drama</t>
+        </is>
+      </c>
+      <c r="F5" s="112" t="inlineStr">
+        <is>
+          <t>02/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="125" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H5" s="125">
+        <f>G5/30</f>
+        <v/>
+      </c>
+      <c r="I5" s="125" t="n"/>
+      <c r="J5" s="112" t="inlineStr">
+        <is>
+          <t>Không có</t>
+        </is>
+      </c>
+      <c r="K5" s="112" t="inlineStr">
+        <is>
+          <t>Tăng rất nhanh. Là app "thông tin" về phim → cần xem kỹ nội dung có vi phạm bản quyền không</t>
+        </is>
+      </c>
+      <c r="L5" s="113" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=infoguide.movies.trailers.dramas.tvshows.webseries</t>
+        </is>
+      </c>
+      <c r="M5" s="113" t="inlineStr">
+        <is>
+          <t>https://www.appbrain.com/app/movies-drama-tv-series-info/infoguide.movies.trailers.dramas.tvshows.webseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="115" t="inlineStr">
+        <is>
+          <t>Themes: Wallpaper &amp; Widgets</t>
+        </is>
+      </c>
+      <c r="C6" s="115" t="inlineStr">
+        <is>
+          <t>com.flyer.theme</t>
+        </is>
+      </c>
+      <c r="D6" s="115" t="inlineStr">
+        <is>
+          <t>ImoDevel</t>
+        </is>
+      </c>
+      <c r="E6" s="115" t="inlineStr">
+        <is>
+          <t>Theme, widget, icon</t>
+        </is>
+      </c>
+      <c r="F6" s="115" t="inlineStr">
+        <is>
+          <t>02/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="126" t="n">
+        <v>640000</v>
+      </c>
+      <c r="H6" s="126">
+        <f>G6/30</f>
+        <v/>
+      </c>
+      <c r="I6" s="126" t="n"/>
+      <c r="J6" s="115" t="inlineStr">
+        <is>
+          <t>Theme icon &amp; widget (dòng 9, 122, 203)</t>
+        </is>
+      </c>
+      <c r="K6" s="115" t="inlineStr">
+        <is>
+          <t>App khác hoàn toàn, nhưng cùng ngách đã có</t>
+        </is>
+      </c>
+      <c r="L6" s="116" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=com.flyer.theme</t>
+        </is>
+      </c>
+      <c r="M6" s="116" t="inlineStr">
+        <is>
+          <t>https://www.appbrain.com/app/themes-wallpaper-widgets/com.flyer.theme</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="112" t="inlineStr">
+        <is>
+          <t>Dootalk: AI Chat</t>
+        </is>
+      </c>
+      <c r="C7" s="112" t="inlineStr">
+        <is>
+          <t>com.dootalk.vibe</t>
+        </is>
+      </c>
+      <c r="D7" s="112" t="inlineStr">
+        <is>
+          <t>M COYLE LLC</t>
+        </is>
+      </c>
+      <c r="E7" s="112" t="inlineStr">
+        <is>
+          <t>AI chat nhân vật</t>
+        </is>
+      </c>
+      <c r="F7" s="112" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="G7" s="125" t="n">
+        <v>410000</v>
+      </c>
+      <c r="H7" s="125">
+        <f>G7/30</f>
+        <v/>
+      </c>
+      <c r="I7" s="125" t="n"/>
+      <c r="J7" s="112" t="inlineStr">
+        <is>
+          <t>AI chat / bạn đồng hành (dòng 84, 100, 206…)</t>
+        </is>
+      </c>
+      <c r="K7" s="112" t="inlineStr">
+        <is>
+          <t>4.69★ / 25K đánh giá; nội dung mức "High Maturity"</t>
+        </is>
+      </c>
+      <c r="L7" s="113" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=com.dootalk.vibe</t>
+        </is>
+      </c>
+      <c r="M7" s="113" t="inlineStr">
+        <is>
+          <t>https://www.appbrain.com/app/dootalk%EF%BC%9Aai-chat/com.dootalk.vibe</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="115" t="inlineStr">
+        <is>
+          <t>Hype AI – AI Photo &amp; Video</t>
+        </is>
+      </c>
+      <c r="C8" s="115" t="inlineStr">
+        <is>
+          <t>com.ai.hype</t>
+        </is>
+      </c>
+      <c r="D8" s="115" t="inlineStr">
+        <is>
+          <t>ORIGO Game</t>
+        </is>
+      </c>
+      <c r="E8" s="115" t="inlineStr">
+        <is>
+          <t>AI ảnh → video (Seedance 2.0)</t>
+        </is>
+      </c>
+      <c r="F8" s="115" t="inlineStr">
+        <is>
+          <t>02/2026</t>
+        </is>
+      </c>
+      <c r="G8" s="126" t="n">
+        <v>330000</v>
+      </c>
+      <c r="H8" s="126">
+        <f>G8/30</f>
+        <v/>
+      </c>
+      <c r="I8" s="126" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="J8" s="115" t="inlineStr">
+        <is>
+          <t>AI tạo ảnh (dòng 182, 195, 297)</t>
+        </is>
+      </c>
+      <c r="K8" s="115" t="inlineStr">
+        <is>
+          <t>#9 Photography; có cả iOS</t>
+        </is>
+      </c>
+      <c r="L8" s="116" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=com.ai.hype</t>
+        </is>
+      </c>
+      <c r="M8" s="116" t="inlineStr">
+        <is>
+          <t>https://www.appbrain.com/app/hype-ai-ai-photo-video/com.ai.hype</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="112" t="inlineStr">
+        <is>
+          <t>The Choicer Voicer</t>
+        </is>
+      </c>
+      <c r="C9" s="112" t="inlineStr">
+        <is>
+          <t>com.snaketapt.runer.sortblasty</t>
+        </is>
+      </c>
+      <c r="D9" s="112" t="inlineStr">
+        <is>
+          <t>SeweSol Game</t>
+        </is>
+      </c>
+      <c r="E9" s="112" t="inlineStr">
+        <is>
+          <t>Game điều khiển bằng giọng nói</t>
+        </is>
+      </c>
+      <c r="F9" s="112" t="inlineStr">
+        <is>
+          <t>08/2026</t>
+        </is>
+      </c>
+      <c r="G9" s="125" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H9" s="125">
+        <f>G9/30</f>
+        <v/>
+      </c>
+      <c r="I9" s="125" t="n"/>
+      <c r="J9" s="112" t="inlineStr">
+        <is>
+          <t>Không có</t>
+        </is>
+      </c>
+      <c r="K9" s="112" t="inlineStr">
+        <is>
+          <t>Là game (Simulation); nhiều bản nhái cùng tên → trend đang nóng</t>
+        </is>
+      </c>
+      <c r="L9" s="113" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=com.snaketapt.runer.sortblasty</t>
+        </is>
+      </c>
+      <c r="M9" s="113" t="inlineStr">
+        <is>
+          <t>https://www.appbrain.com/app/the-choicer-voicer/com.snaketapt.runer.sortblasty</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="115" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="115" t="inlineStr">
+        <is>
+          <t>Bug Filter – Insect Prank</t>
+        </is>
+      </c>
+      <c r="C10" s="115" t="inlineStr">
+        <is>
+          <t>com.nexify.insect.funny.prank.filter.bug.camera</t>
+        </is>
+      </c>
+      <c r="D10" s="115" t="inlineStr">
+        <is>
+          <t>Themes Design Apps</t>
+        </is>
+      </c>
+      <c r="E10" s="115" t="inlineStr">
+        <is>
+          <t>Filter prank côn trùng</t>
+        </is>
+      </c>
+      <c r="F10" s="115" t="inlineStr">
+        <is>
+          <t>01/2026</t>
+        </is>
+      </c>
+      <c r="G10" s="126" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H10" s="126">
+        <f>G10/30</f>
+        <v/>
+      </c>
+      <c r="I10" s="126" t="n">
+        <v>270000</v>
+      </c>
+      <c r="J10" s="115" t="inlineStr">
+        <is>
+          <t>Filter challenge / prank (dòng 116, 117…)</t>
+        </is>
+      </c>
+      <c r="K10" s="115" t="inlineStr">
+        <is>
+          <t>4.05★; cùng nhà phát triển với app Falling Loop (dòng 117)</t>
+        </is>
+      </c>
+      <c r="L10" s="116" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=com.nexify.insect.funny.prank.filter.bug.camera</t>
+        </is>
+      </c>
+      <c r="M10" s="116" t="inlineStr">
+        <is>
+          <t>https://www.appbrain.com/app/bug-filter-insect-prank/com.nexify.insect.funny.prank.filter.bug.camera</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="112" t="inlineStr">
+        <is>
+          <t>Smart AI Video – Veozi</t>
+        </is>
+      </c>
+      <c r="C11" s="112" t="inlineStr">
+        <is>
+          <t>com.veozi.video.app</t>
+        </is>
+      </c>
+      <c r="D11" s="112" t="inlineStr">
+        <is>
+          <t>Eanderfty. P Lakiop</t>
+        </is>
+      </c>
+      <c r="E11" s="112" t="inlineStr">
+        <is>
+          <t>AI ảnh → video</t>
+        </is>
+      </c>
+      <c r="F11" s="112" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="G11" s="125" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H11" s="125">
+        <f>G11/30</f>
+        <v/>
+      </c>
+      <c r="I11" s="125" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J11" s="112" t="inlineStr">
+        <is>
+          <t>AI tạo ảnh (dòng 297)</t>
+        </is>
+      </c>
+      <c r="K11" s="112" t="inlineStr">
+        <is>
+          <t>Toàn bộ 45K lượt tải trong 30 ngày → mới lên</t>
+        </is>
+      </c>
+      <c r="L11" s="113" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=com.veozi.video.app</t>
+        </is>
+      </c>
+      <c r="M11" s="113" t="inlineStr">
+        <is>
+          <t>https://www.appbrain.com/app/smart-ai-video-veozi/com.veozi.video.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="127" t="inlineStr">
+        <is>
+          <t>Đã kiểm tra nhưng loại:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="128" t="inlineStr">
+        <is>
+          <t>• CoinIn – Coin Scan Identifier: ra mắt 06/2025 (quá 1 năm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="128" t="inlineStr">
+        <is>
+          <t>• AI Video App: Make Trend Video: ra mắt 01/2025, chỉ 250 lượt tải/30 ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="128" t="inlineStr">
+        <is>
+          <t>• Movira AI: ra mắt 04/2026 nhưng ~220 install/ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="128" t="inlineStr">
+        <is>
+          <t>• Momo Scary Video Call: ra mắt 02/2026 nhưng ~600 install/ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="128" t="inlineStr">
+        <is>
+          <t>• Funny Insect Prank Filter Game: ra mắt 01/2026 nhưng ~300 install/ngày</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId14"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -57264,7 +57859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
